--- a/data_lake/macro/USA/US Consumer Confidence.xlsx
+++ b/data_lake/macro/USA/US Consumer Confidence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388E99D5-3277-4BD9-A541-46029131B6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF1481E-A349-4924-BD08-58BA8CA985CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
   </bookViews>
@@ -521,14 +521,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0F7D99-AC79-884E-BA11-A70B8FD1EA94}">
   <dimension ref="A1:G680"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.54296875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="10.90625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.54296875" style="7"/>
+    <col min="5" max="7" width="9.1796875" style="11"/>
+    <col min="8" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/data_lake/macro/USA/US Consumer Confidence.xlsx
+++ b/data_lake/macro/USA/US Consumer Confidence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF1481E-A349-4924-BD08-58BA8CA985CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B37A022-C946-4338-ADC4-A5FA363E9C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
   </bookViews>
@@ -520,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0F7D99-AC79-884E-BA11-A70B8FD1EA94}">
-  <dimension ref="A1:G680"/>
+  <dimension ref="A1:G681"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="8" bestFit="1" customWidth="1"/>
@@ -14740,7 +14740,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D643" s="10" t="str">
-        <f t="shared" ref="D643:D680" si="10">IF(
+        <f t="shared" ref="D643:D681" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -15646,11 +15646,32 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E680" s="11">
+        <v>90.8</v>
+      </c>
       <c r="F680" s="11">
-        <v>92.1</v>
+        <v>92.4</v>
       </c>
       <c r="G680" s="11">
-        <v>91.2</v>
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A681" s="8">
+        <v>46235</v>
+      </c>
+      <c r="B681" s="8">
+        <v>46259</v>
+      </c>
+      <c r="C681" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D681" s="10" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G681" s="11">
+        <v>90.8</v>
       </c>
     </row>
   </sheetData>
